--- a/artfynd/S 3260-2025 artfynd.xlsx
+++ b/artfynd/S 3260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102632060</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1051,6 +1066,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17348495</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1162,6 +1182,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68874807</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1281,6 +1306,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102174550</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1402,6 +1432,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15521234</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1532,6 +1567,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15677314</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1643,6 +1683,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56123541</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1749,6 +1794,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78593942</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1872,6 +1922,11 @@
           <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910682</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2002,6 +2057,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118245619</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2118,6 +2178,11 @@
           <t>Personlig inventering NES</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98554952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2236,6 +2301,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94290280</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2354,6 +2424,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94291572</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2472,6 +2547,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94291592</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2607,6 +2687,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6183296</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2742,6 +2827,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6183297</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2877,6 +2967,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6183867</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3012,6 +3107,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6183868</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3123,6 +3223,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6840371</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3254,6 +3359,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187729</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3385,6 +3495,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187738</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3516,6 +3631,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7187742</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3627,6 +3747,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16352344</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3733,6 +3858,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62001011</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3843,6 +3973,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866151</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3953,6 +4088,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866152</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4063,6 +4203,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866154</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4173,6 +4318,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866155</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4283,6 +4433,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866156</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4398,6 +4553,11 @@
           <t>ÅGP Fältgentiana C-län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88866184</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4512,6 +4672,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125939822</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4618,6 +4783,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57458470</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4730,6 +4900,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133306072</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4844,6 +5019,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86881303</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4963,6 +5143,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134975418</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5074,6 +5259,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133514045</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5207,6 +5397,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132639243</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5327,6 +5522,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54746683</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5438,6 +5638,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62001100</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5544,6 +5749,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090649</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5650,6 +5860,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56090651</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5752,8 +5967,58 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56124325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3260-2025 artfynd.xlsx
+++ b/artfynd/S 3260-2025 artfynd.xlsx
@@ -5030,7 +5030,7 @@
         <v>134975418</v>
       </c>
       <c r="B37" t="n">
-        <v>57386</v>
+        <v>57391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
